--- a/artfynd/A 20623-2021 artfynd.xlsx
+++ b/artfynd/A 20623-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20623-2021 artfynd.xlsx
+++ b/artfynd/A 20623-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74464266</v>
       </c>
       <c r="B2" t="n">
-        <v>101692</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526342.1384606124</v>
+        <v>526342</v>
       </c>
       <c r="R2" t="n">
-        <v>6311778.205926383</v>
+        <v>6311778</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -744,19 +739,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1991-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -800,12 +785,7 @@
         <v>74885012</v>
       </c>
       <c r="B3" t="n">
-        <v>102093</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526542.1319121871</v>
+        <v>526542</v>
       </c>
       <c r="R3" t="n">
-        <v>6311780.568465808</v>
+        <v>6311781</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -870,19 +850,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1991-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 20623-2021 artfynd.xlsx
+++ b/artfynd/A 20623-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74464266</v>
       </c>
       <c r="B2" t="n">
-        <v>104061</v>
+        <v>104070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74885012</v>
       </c>
       <c r="B3" t="n">
-        <v>104466</v>
+        <v>104475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20623-2021 artfynd.xlsx
+++ b/artfynd/A 20623-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74464266</v>
       </c>
       <c r="B2" t="n">
-        <v>104070</v>
+        <v>104073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74885012</v>
       </c>
       <c r="B3" t="n">
-        <v>104475</v>
+        <v>104478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20623-2021 artfynd.xlsx
+++ b/artfynd/A 20623-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74464266</v>
       </c>
       <c r="B2" t="n">
-        <v>104073</v>
+        <v>104100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74885012</v>
       </c>
       <c r="B3" t="n">
-        <v>104478</v>
+        <v>104505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20623-2021 artfynd.xlsx
+++ b/artfynd/A 20623-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74464266</v>
       </c>
       <c r="B2" t="n">
-        <v>104100</v>
+        <v>104106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74885012</v>
       </c>
       <c r="B3" t="n">
-        <v>104505</v>
+        <v>104511</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20623-2021 artfynd.xlsx
+++ b/artfynd/A 20623-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74464266</v>
       </c>
       <c r="B2" t="n">
-        <v>104106</v>
+        <v>104113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74885012</v>
       </c>
       <c r="B3" t="n">
-        <v>104511</v>
+        <v>104518</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20623-2021 artfynd.xlsx
+++ b/artfynd/A 20623-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74464266</v>
       </c>
       <c r="B2" t="n">
-        <v>104113</v>
+        <v>104117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74885012</v>
       </c>
       <c r="B3" t="n">
-        <v>104518</v>
+        <v>104522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20623-2021 artfynd.xlsx
+++ b/artfynd/A 20623-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74464266</v>
       </c>
       <c r="B2" t="n">
-        <v>104117</v>
+        <v>104124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74885012</v>
       </c>
       <c r="B3" t="n">
-        <v>104522</v>
+        <v>104529</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20623-2021 artfynd.xlsx
+++ b/artfynd/A 20623-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74464266</v>
       </c>
       <c r="B2" t="n">
-        <v>104127</v>
+        <v>104132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74885012</v>
       </c>
       <c r="B3" t="n">
-        <v>104532</v>
+        <v>104537</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20623-2021 artfynd.xlsx
+++ b/artfynd/A 20623-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74464266</v>
       </c>
       <c r="B2" t="n">
-        <v>104132</v>
+        <v>104140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74885012</v>
       </c>
       <c r="B3" t="n">
-        <v>104537</v>
+        <v>104545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20623-2021 artfynd.xlsx
+++ b/artfynd/A 20623-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74464266</v>
       </c>
       <c r="B2" t="n">
-        <v>104140</v>
+        <v>104150</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74885012</v>
       </c>
       <c r="B3" t="n">
-        <v>104545</v>
+        <v>104555</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
